--- a/Packages/cn.etetet.yiuilubangen/Luban/Localhost/Datas/StartZone.xlsx
+++ b/Packages/cn.etetet.yiuilubangen/Luban/Localhost/Datas/StartZone.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12525"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="StartZoneConfig" sheetId="1" r:id="rId1"/>
@@ -27,12 +27,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
   <si>
     <t>##var</t>
   </si>
   <si>
     <t>Id</t>
+  </si>
+  <si>
+    <t>ZoneType</t>
   </si>
   <si>
     <t>DBConnection</t>
@@ -79,6 +82,12 @@
   <si>
     <t>路由区</t>
   </si>
+  <si>
+    <t>ET1000</t>
+  </si>
+  <si>
+    <t>账号登陆服</t>
+  </si>
 </sst>
 </file>
 
@@ -90,7 +99,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -106,12 +115,6 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
@@ -586,13 +589,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -601,122 +607,119 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -730,11 +733,8 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1090,14 +1090,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XFD6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
+  <dimension ref="A1:XFD7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="21.125" style="4" customWidth="1"/>
     <col min="2" max="2" width="12.625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="17.5" style="5" customWidth="1"/>
-    <col min="4" max="5" width="21" style="5" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="4"/>
+    <col min="3" max="4" width="17.5" style="5" customWidth="1"/>
+    <col min="5" max="6" width="21" style="5" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:16384">
@@ -1116,7 +1116,9 @@
       <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4"/>
+      <c r="F1" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
       <c r="I1" s="4"/>
@@ -17498,21 +17500,23 @@
     </row>
     <row r="2" s="2" customFormat="1" spans="1:16384">
       <c r="A2" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
-      <c r="F2" s="4"/>
+      <c r="F2" s="6" t="s">
+        <v>8</v>
+      </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
@@ -33894,13 +33898,13 @@
     </row>
     <row r="3" s="1" customFormat="1" spans="1:16384">
       <c r="A3" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>10</v>
@@ -33908,7 +33912,9 @@
       <c r="E3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="4"/>
+      <c r="F3" s="6" t="s">
+        <v>12</v>
+      </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
@@ -50288,12 +50294,12 @@
       <c r="XFC3" s="4"/>
       <c r="XFD3" s="4"/>
     </row>
-    <row r="4" spans="2:5">
+    <row r="4" spans="2:6">
       <c r="B4" s="7">
         <v>1</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>12</v>
+      <c r="C4" s="7">
+        <v>1</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>13</v>
@@ -50301,28 +50307,36 @@
       <c r="E4" s="7" t="s">
         <v>14</v>
       </c>
+      <c r="F4" s="7" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="5" spans="2:5">
-      <c r="B5" s="8">
+    <row r="5" spans="2:6">
+      <c r="B5" s="5">
         <v>2</v>
       </c>
-      <c r="C5" s="7"/>
+      <c r="C5" s="7">
+        <v>2</v>
+      </c>
       <c r="D5" s="7"/>
-      <c r="E5" s="7" t="s">
-        <v>15</v>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="6" s="3" customFormat="1" spans="1:16384">
       <c r="A6" s="4"/>
-      <c r="B6" s="8">
+      <c r="B6" s="5">
         <v>3</v>
       </c>
-      <c r="C6" s="7"/>
+      <c r="C6" s="7">
+        <v>3</v>
+      </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="7" t="s">
-        <v>16</v>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7" t="s">
+        <v>17</v>
       </c>
-      <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
@@ -66702,6 +66716,23 @@
       <c r="XFC6" s="4"/>
       <c r="XFD6" s="4"/>
     </row>
+    <row r="7" spans="2:6">
+      <c r="B7" s="5">
+        <v>1000</v>
+      </c>
+      <c r="C7" s="5">
+        <v>4</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Packages/cn.etetet.yiuilubangen/Luban/Localhost/Datas/StartZone.xlsx
+++ b/Packages/cn.etetet.yiuilubangen/Luban/Localhost/Datas/StartZone.xlsx
@@ -35,9 +35,6 @@
     <t>Id</t>
   </si>
   <si>
-    <t>ZoneType</t>
-  </si>
-  <si>
     <t>DBConnection</t>
   </si>
   <si>
@@ -45,6 +42,9 @@
   </si>
   <si>
     <t>Desc</t>
+  </si>
+  <si>
+    <t>ZoneType</t>
   </si>
   <si>
     <t>##type</t>
@@ -1090,17 +1090,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XFD7"/>
+  <dimension ref="A1:XFC7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="21.125" style="4" customWidth="1"/>
     <col min="2" max="2" width="12.625" style="5" customWidth="1"/>
-    <col min="3" max="4" width="17.5" style="5" customWidth="1"/>
-    <col min="5" max="6" width="21" style="5" customWidth="1"/>
+    <col min="3" max="3" width="17.5" style="5" customWidth="1"/>
+    <col min="4" max="5" width="21" style="5" customWidth="1"/>
+    <col min="6" max="6" width="17.5" style="5" customWidth="1"/>
     <col min="7" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:16384">
+    <row r="1" s="1" customFormat="1" spans="1:16383">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -17496,9 +17497,8 @@
       <c r="XFA1" s="4"/>
       <c r="XFB1" s="4"/>
       <c r="XFC1" s="4"/>
-      <c r="XFD1" s="4"/>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:16384">
+    <row r="2" s="2" customFormat="1" spans="1:16383">
       <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
@@ -17506,7 +17506,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>8</v>
@@ -17515,7 +17515,7 @@
         <v>8</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
@@ -33894,9 +33894,8 @@
       <c r="XFA2" s="4"/>
       <c r="XFB2" s="4"/>
       <c r="XFC2" s="4"/>
-      <c r="XFD2" s="4"/>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:16384">
+    <row r="3" s="1" customFormat="1" spans="1:16383">
       <c r="A3" s="4" t="s">
         <v>9</v>
       </c>
@@ -33904,16 +33903,16 @@
         <v>1</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
@@ -50292,50 +50291,49 @@
       <c r="XFA3" s="4"/>
       <c r="XFB3" s="4"/>
       <c r="XFC3" s="4"/>
-      <c r="XFD3" s="4"/>
     </row>
     <row r="4" spans="2:6">
       <c r="B4" s="7">
         <v>1</v>
       </c>
-      <c r="C4" s="7">
-        <v>1</v>
+      <c r="C4" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>15</v>
+      <c r="F4" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="2:6">
       <c r="B5" s="5">
         <v>2</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="7">
         <v>2</v>
       </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7" t="s">
-        <v>16</v>
-      </c>
     </row>
-    <row r="6" s="3" customFormat="1" spans="1:16384">
+    <row r="6" s="3" customFormat="1" spans="1:16383">
       <c r="A6" s="4"/>
       <c r="B6" s="5">
         <v>3</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="7">
         <v>3</v>
-      </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7" t="s">
-        <v>17</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -66714,23 +66712,22 @@
       <c r="XFA6" s="4"/>
       <c r="XFB6" s="4"/>
       <c r="XFC6" s="4"/>
-      <c r="XFD6" s="4"/>
     </row>
     <row r="7" spans="2:6">
       <c r="B7" s="5">
         <v>1000</v>
       </c>
-      <c r="C7" s="5">
-        <v>4</v>
+      <c r="C7" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>19</v>
+      <c r="F7" s="5">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
